--- a/originales/respuestas/2025/01. Calificadas/bucle p2/Alcaldía Local De Usme.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p2/Alcaldía Local De Usme.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Downloads/IIP - Esteban/bucle p2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B19B372-F6D0-4E5B-BD07-96C0E0C3D012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C74BD7F1-7F6A-9444-82D8-D31A4977F50B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{BEBA6F3E-F229-47C6-9D8B-B29A4841AE29}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16680" xr2:uid="{BEBA6F3E-F229-47C6-9D8B-B29A4841AE29}"/>
   </bookViews>
   <sheets>
     <sheet name="Entidad" sheetId="1" r:id="rId1"/>
@@ -141,7 +141,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -153,17 +153,28 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF434343"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF434343"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -255,10 +266,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -278,8 +290,12 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -594,9 +610,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6341B579-35D1-4EC8-9795-4FBED26CECB5}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="A1:Q7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="42" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -649,7 +665,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>17</v>
       </c>
@@ -668,35 +684,35 @@
         <v>21</v>
       </c>
       <c r="H2" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>22</v>
       </c>
       <c r="J2" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>23</v>
       </c>
       <c r="L2" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>24</v>
       </c>
       <c r="N2" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O2" s="4" t="s">
         <v>25</v>
       </c>
       <c r="P2" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q2" s="4"/>
     </row>
-    <row r="3" spans="1:17" ht="237.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" ht="266" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>17</v>
       </c>
@@ -715,35 +731,35 @@
         <v>21</v>
       </c>
       <c r="H3" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>22</v>
       </c>
       <c r="J3" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>23</v>
       </c>
       <c r="L3" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M3" s="4" t="s">
         <v>24</v>
       </c>
       <c r="N3" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O3" s="4" t="s">
         <v>25</v>
       </c>
       <c r="P3" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q3" s="4"/>
     </row>
-    <row r="4" spans="1:17" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>17</v>
       </c>
@@ -762,35 +778,35 @@
         <v>21</v>
       </c>
       <c r="H4" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>22</v>
       </c>
       <c r="J4" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>23</v>
       </c>
       <c r="L4" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>24</v>
       </c>
       <c r="N4" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O4" s="4" t="s">
         <v>25</v>
       </c>
       <c r="P4" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q4" s="4"/>
     </row>
-    <row r="5" spans="1:17" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>17</v>
       </c>
@@ -804,42 +820,42 @@
       <c r="E5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="7" t="s">
         <v>30</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>21</v>
       </c>
       <c r="H5" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>22</v>
       </c>
       <c r="J5" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K5" s="5" t="s">
         <v>23</v>
       </c>
       <c r="L5" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M5" s="5" t="s">
         <v>24</v>
       </c>
       <c r="N5" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O5" s="5" t="s">
         <v>25</v>
       </c>
       <c r="P5" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q5" s="5"/>
     </row>
-    <row r="6" spans="1:17" ht="237.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" ht="266" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>17</v>
       </c>
@@ -860,35 +876,35 @@
         <v>21</v>
       </c>
       <c r="H6" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>22</v>
       </c>
       <c r="J6" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K6" s="5" t="s">
         <v>23</v>
       </c>
       <c r="L6" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M6" s="5" t="s">
         <v>24</v>
       </c>
       <c r="N6" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O6" s="5" t="s">
         <v>25</v>
       </c>
       <c r="P6" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q6" s="5"/>
     </row>
-    <row r="7" spans="1:17" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>17</v>
       </c>
@@ -909,37 +925,38 @@
         <v>21</v>
       </c>
       <c r="H7" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>22</v>
       </c>
       <c r="J7" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>23</v>
       </c>
       <c r="L7" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M7" s="5" t="s">
         <v>24</v>
       </c>
       <c r="N7" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O7" s="5" t="s">
         <v>25</v>
       </c>
       <c r="P7" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q7" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" xr:uid="{55F517BF-600F-41D9-AF0B-6A4EF7D4B6B5}"/>
+    <hyperlink ref="F5" r:id="rId2" xr:uid="{BCC90DE0-9C55-E24D-866F-7A4630E3DCA3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
